--- a/healthcare_forms/049_dietary_communication_form--healthcare_forms.xlsx
+++ b/healthcare_forms/049_dietary_communication_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Food Allergies</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Patient's Food Allergies</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select all the food allergies the patient has</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>restrictions</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dietary Restrictions</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all the medical conditions the patient has</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>dietary_preferences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Dietary Preferences</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select all the dietary preferences the patient has</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>food_preferences</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Food Preferences</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Emergency Contact Information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Provide the contact information for the patient's emergency contact</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,43 +623,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dietary_restrictions</t>
+          <t>date_and_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dietary Preferences</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date and Time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the date and time the patient needs to take their medication</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>food_intolerances</t>
+          <t>medical_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Food Intolerances</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Medical Notes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Add any additional medical notes about the patient's condition</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_notes</t>
+          <t>emergency_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Notes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Emergency Phone Number</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the phone number of the emergency contact</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -689,7 +717,11 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the email of the patient's emergency contact</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>emergency_notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Medical Notes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Add any additional medical notes about the patient</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter the date the patient needs to take their medication</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter the time the patient needs to take their medication</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,435 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>emergency_contact_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select all the emergency contacts</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>date_time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>medical_notes_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Medical Notes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>emergency_contact_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>emergency_phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>emergency_email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_notes_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Medical Notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date_time_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>emergency_contact_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>emergency_phone_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>emergency_email_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>medical_notes_4</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Medical Notes</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>date_3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>time_3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1216,9 +850,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +880,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Eggs</t>
         </is>
       </c>
     </row>
@@ -1263,223 +897,223 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>food_preferences_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Gluten</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>food_preferences_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dietary_restrictions_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dietary_restrictions_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>food_intolerances_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High Cholesterol</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>food_intolerances_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>emergency_contact_2_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>kosher</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Kosher</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>emergency_contact_2_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emergency_contact_3_choices</t>
+          <t>emergency_contact_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,7 +1130,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_3_choices</t>
+          <t>emergency_contact_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
